--- a/data/test_Gaza20249.xlsx
+++ b/data/test_Gaza20249.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\missing-persons-armed-conflict-telegram-pipeline\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0844C79-8709-49B1-8192-7900B332FF4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998D4CD4-623B-46BA-8155-47F5F629FD48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{E06811FE-69FF-476D-82E2-6FB5A83AF306}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="test_df_Gaza20249" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">test_df_Gaza20249!$A$1:$G$303</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">test_df_Gaza20249!$A$1:$G$295</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="586">
   <si>
     <t xml:space="preserve"> عاج ل مناشدات من العائلات في عمارة سكيك مقابل مخبز العائلات غرب مدينة غزة للصليب الاحمر لانقاذ المصابين بعد استهدافهم من قبل الاحتلال واطلاق النار على كل من يتحرك لمساعدتهم </t>
   </si>
@@ -116,13 +116,6 @@
 السلام عليكم اخوي حمزة دار اهلي انقصفت دار الرياعي ولاد اخواتي تخت الردم و اهلي الناجين عند جيرانا
 في غزة شارع ابوحصيرة  اتواصلت مع الهلال الاحمر حكالنا ملهمش شغل بغزة
 بدنا اسعاف يروح ع المكان ضروري مرت اخوية وابن عمي متصاوبين</t>
-  </si>
-  <si>
-    <t>ارجو انك تنزل مناشدة تم وجد كرت مؤن في شارع السوق في النصيرات لعائلة ابو فنونة للتواصل على الرقم 0595961603</t>
-  </si>
-  <si>
-    <t>ارجو انك تنزل مناشدة تم وجد كرت مؤن في شارع السوق في النصيرات لعائلة ابو فنونة 
-للتواصل على الرقم 0595961603</t>
   </si>
   <si>
     <t>تم فقد محفظة بالسوق الغربي في رفح بها  مبلغ من المال وهوية وتامين ورقة مدرسة كرت تموين لمن يجد محتوياتها يرجى الاتصال على رائف اسعيد صافي 0595266365</t>
@@ -138,62 +131,11 @@
 0595266365</t>
   </si>
   <si>
-    <t>لقيناه بالشارع محيط دوار زعرب موجود عنا بالبيت تواصلو ع الرقم 0599630128</t>
-  </si>
-  <si>
-    <t>لقيناه بالشارع محيط دوار زعرب 
-موجود عنا بالبيت 
-تواصلو ع الرقم 0599630128</t>
-  </si>
-  <si>
-    <t>هدا الطفل ضايع من الساعة ١٠ الصبح في رفح منطقة دوار زعرب اسمة رشاد محمد رشاد السرسك العمر سنتين ونص هي رقم اهلو 0594351018</t>
-  </si>
-  <si>
-    <t>هدا الطفل ضايع من الساعة ١٠ الصبح في رفح
-منطقة دوار زعرب
-اسمة
-رشاد محمد رشاد السرسك 
-العمر سنتين ونص
-هي رقم اهلو 0594351018</t>
-  </si>
-  <si>
-    <t>جثة شهيد عند كراج رفح في شارع شبير بخانيونس من عائلة الصعيدي من غزة</t>
-  </si>
-  <si>
     <t xml:space="preserve">اعلنا عن فقدانه سابقا استشهاد الاستاذ   محمد حسن المصري بعد انتشال جثمانه من شمال بيت لاهيا بعد ثلاث ايام من اصابته </t>
   </si>
   <si>
     <t>اعلنا عن فقدانه سابقآ إستشهاد الأستاذ / محمد حسن المصري
 بعد إنتشال جثمانه من شمال بيت لاهيا بعد ثلاث أيام من إصابته.</t>
-  </si>
-  <si>
-    <t>مناشدة عاجلة انا في مدينة حمد والوضع صعب جدا بحسب ما افاد الجيش ان مدينة حمد مدينة قتال عنيفة نرجو من الهلال والصليب الاحمر التنسيق لاخلائنا الفوري من مدينة حمد علما ان بالمدينة اكثر من 5000 مواطن</t>
-  </si>
-  <si>
-    <t>مناشدة عاجلة
-انا في مدينة حمد والوضع صعب جدا
-بحسب ما افاد الجيش ان مدينة حمد مدينة قتال عنيفة نرجو من الهلال والصليب  الاحمر التنسيق لاخلائنا الفوري من مدينة حمد علما ان بالمدينة اكثر من 5000 مواطن</t>
-  </si>
-  <si>
-    <t>كما وصلنا جماعة الخير اخوي محمد حسن المصري من البارح طالع الصبح ع بيتنا الموجود في الشيماء قبل ما ينزلوا المظلات القريبة من القرية البدوية اي حدا شافه او بعرف اي شي عنه يتواصل معي هان او يرن ع ابوي رقم 0599915279</t>
-  </si>
-  <si>
-    <t>كما وصلنا
-جماعة الخير 
-اخوي محمد حسن المصري
-من البارح طالع الصبح ع بيتنا الموجود في الشيماء قبل ما ينزلوا المظلات القريبة من القرية البدوية
-اي حدا شافه أو بعرف اي شي عنه 
-يتواصل معي هان 
-أو يرن ع ابوي رقم 0599915279</t>
-  </si>
-  <si>
-    <t>اخي فقدت هويه بسم محمود ابو يوسف ان حدا بلغ انو وجدها حاكيني وشكراا 0567829448</t>
-  </si>
-  <si>
-    <t>اخي فقدت هويه بسم محمود ابو يوسف 
-ان حدا بلغ انو وجدها حاكيني
-وشكراا
-0567829448</t>
   </si>
   <si>
     <t>فقدان هوية شخصية باسم   جادالله محمد القرا الرجاء ممن عثر او يعثر عليها التواصل على الرقم 0599687606 او0595846300</t>
@@ -2459,13 +2401,6 @@
   </si>
   <si>
     <t>برجاء النشر العثور علي طفل علي صلاح الدين موجود طرف ابو كريم موجود عند ابو كريم 0567008133 الزوايدة</t>
-  </si>
-  <si>
-    <t>السلام عليكم ورحمة اللة وبركاته 
-يا اهل الخير يا اهل الكرم والجود يا اهل العزة والكرامة والشموخ نحتاج من الله ثم منكم المساعدة لعلاج ابنتي مريضة لتهاب الكبد A تحتاج الي علاج ايضا الي حاجات حلوة او سكريات و ماء نقي نظيف ايضا بعض التحاليل استحلفكم بالله تساعدني بتوفر الازم هذا رقم للتواصل 0594443318</t>
-  </si>
-  <si>
-    <t>السلام عليكم ورحمة اللة وبركاته يا اهل الخير يا اهل الكرم والجود يا اهل العزة والكرامة والشموخ نحتاج من الله ثم منكم المساعدة لعلاج ابنتي مريضة لتهاب الكبد a تحتاج الي علاج ايضا الي حاجات حلوة او سكريات و ماء نقي نظيف ايضا بعض التحاليل استحلفكم بالله تساعدني بتوفر الازم هذا رقم للتواصل 0594443318</t>
   </si>
   <si>
     <t>⚪️ كما وصل لنا 
@@ -3373,7 +3308,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F33CD2C8-CD88-4DD5-9FF5-279A63800069}">
-  <dimension ref="A1:G303"/>
+  <dimension ref="A1:G295"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.5546875" style="1"/>
@@ -3381,25 +3316,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="C1" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="D1" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="E1" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="F1" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="G1" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -3410,10 +3345,10 @@
         <v>45285.787581018521</v>
       </c>
       <c r="C2" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="D2" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="E2">
         <v>6052</v>
@@ -3433,10 +3368,10 @@
         <v>45285.996805555558</v>
       </c>
       <c r="C3" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="D3" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="E3">
         <v>3362</v>
@@ -3456,10 +3391,10 @@
         <v>45286.551550925928</v>
       </c>
       <c r="C4" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="D4" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="E4">
         <v>3606</v>
@@ -3479,10 +3414,10 @@
         <v>45286.887048611112</v>
       </c>
       <c r="C5" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="D5" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E5">
         <v>2894</v>
@@ -3502,10 +3437,10 @@
         <v>45287.490115740737</v>
       </c>
       <c r="C6" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="D6" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="E6">
         <v>2670</v>
@@ -3525,10 +3460,10 @@
         <v>45288.56931712963</v>
       </c>
       <c r="C7" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D7" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="E7">
         <v>3163</v>
@@ -3548,10 +3483,10 @@
         <v>45288.914282407408</v>
       </c>
       <c r="C8" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="D8" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="E8">
         <v>2924</v>
@@ -3571,10 +3506,10 @@
         <v>45289.466064814813</v>
       </c>
       <c r="C9" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="D9" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="E9">
         <v>3112</v>
@@ -3594,10 +3529,10 @@
         <v>45289.92895833333</v>
       </c>
       <c r="C10" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="D10" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="E10">
         <v>4293</v>
@@ -3617,10 +3552,10 @@
         <v>45290.953796296293</v>
       </c>
       <c r="C11" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="D11" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="E11">
         <v>3401</v>
@@ -3640,10 +3575,10 @@
         <v>45291.754282407397</v>
       </c>
       <c r="C12" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="D12" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="E12">
         <v>3697</v>
@@ -3663,10 +3598,10 @@
         <v>45292.817731481482</v>
       </c>
       <c r="C13" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="D13" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="E13">
         <v>4253</v>
@@ -3686,10 +3621,10 @@
         <v>45294.560729166667</v>
       </c>
       <c r="C14" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="D14" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="E14">
         <v>3550</v>
@@ -3709,10 +3644,10 @@
         <v>45294.925092592603</v>
       </c>
       <c r="C15" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="D15" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="E15">
         <v>3232</v>
@@ -3732,10 +3667,10 @@
         <v>45296.54115740741</v>
       </c>
       <c r="C16" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="D16" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="E16">
         <v>3384</v>
@@ -3755,10 +3690,10 @@
         <v>45297.526666666658</v>
       </c>
       <c r="C17" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="D17" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="E17">
         <v>2796</v>
@@ -3778,10 +3713,10 @@
         <v>45298.017453703702</v>
       </c>
       <c r="C18" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="D18" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E18">
         <v>2991</v>
@@ -3801,10 +3736,10 @@
         <v>45298.716504629629</v>
       </c>
       <c r="C19" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="D19" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="E19">
         <v>3068</v>
@@ -3824,10 +3759,10 @@
         <v>45300.043946759259</v>
       </c>
       <c r="C20" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="D20" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="E20">
         <v>3078</v>
@@ -3847,10 +3782,10 @@
         <v>45300.652303240742</v>
       </c>
       <c r="C21" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="D21" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E21">
         <v>2934</v>
@@ -3873,7 +3808,7 @@
         <v>0</v>
       </c>
       <c r="D22" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="E22">
         <v>3168</v>
@@ -3893,10 +3828,10 @@
         <v>45302.469097222223</v>
       </c>
       <c r="C23" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="D23" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E23">
         <v>3132</v>
@@ -3916,10 +3851,10 @@
         <v>45303.60497685185</v>
       </c>
       <c r="C24" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="D24" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E24">
         <v>2440</v>
@@ -3939,10 +3874,10 @@
         <v>45305.632638888892</v>
       </c>
       <c r="C25" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="D25" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="E25">
         <v>2864</v>
@@ -3962,10 +3897,10 @@
         <v>45306.894050925926</v>
       </c>
       <c r="C26" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="E26">
         <v>3142</v>
@@ -3985,10 +3920,10 @@
         <v>45308.861597222232</v>
       </c>
       <c r="C27" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="D27" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="E27">
         <v>3105</v>
@@ -4008,10 +3943,10 @@
         <v>45311.953356481477</v>
       </c>
       <c r="C28" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="E28">
         <v>2999</v>
@@ -4031,10 +3966,10 @@
         <v>45312.827002314807</v>
       </c>
       <c r="C29" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="D29" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="E29">
         <v>2358</v>
@@ -4054,10 +3989,10 @@
         <v>45313.597893518519</v>
       </c>
       <c r="C30" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="D30" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="E30">
         <v>2138</v>
@@ -4077,10 +4012,10 @@
         <v>45314.628287037027</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="D31" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="E31">
         <v>2363</v>
@@ -4100,10 +4035,10 @@
         <v>45315.387592592589</v>
       </c>
       <c r="C32" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="D32" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="E32">
         <v>2154</v>
@@ -4123,10 +4058,10 @@
         <v>45316.044178240743</v>
       </c>
       <c r="C33" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="D33" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="E33">
         <v>2673</v>
@@ -4146,10 +4081,10 @@
         <v>45316.412835648152</v>
       </c>
       <c r="C34" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="D34" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="E34">
         <v>2377</v>
@@ -4169,10 +4104,10 @@
         <v>45316.820150462961</v>
       </c>
       <c r="C35" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D35" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="E35">
         <v>2703</v>
@@ -4192,10 +4127,10 @@
         <v>45317.575775462959</v>
       </c>
       <c r="C36" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="D36" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="E36">
         <v>2413</v>
@@ -4215,10 +4150,10 @@
         <v>45317.927118055559</v>
       </c>
       <c r="C37" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="D37" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="E37">
         <v>2626</v>
@@ -4238,10 +4173,10 @@
         <v>45318.468472222223</v>
       </c>
       <c r="C38" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="D38" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="E38">
         <v>1989</v>
@@ -4261,10 +4196,10 @@
         <v>45319.00854166667</v>
       </c>
       <c r="C39" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="D39" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="E39">
         <v>2261</v>
@@ -4284,10 +4219,10 @@
         <v>45319.845046296286</v>
       </c>
       <c r="C40" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="D40" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="E40">
         <v>2204</v>
@@ -4307,10 +4242,10 @@
         <v>45319.939085648148</v>
       </c>
       <c r="C41" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="D41" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="E41">
         <v>2304</v>
@@ -4330,10 +4265,10 @@
         <v>45320.860277777778</v>
       </c>
       <c r="C42" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="D42" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E42">
         <v>2544</v>
@@ -4353,10 +4288,10 @@
         <v>45321.704004629632</v>
       </c>
       <c r="C43" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D43" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="E43">
         <v>2559</v>
@@ -4376,10 +4311,10 @@
         <v>45321.862928240742</v>
       </c>
       <c r="C44" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D44" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="E44">
         <v>2766</v>
@@ -4399,10 +4334,10 @@
         <v>45323.804444444453</v>
       </c>
       <c r="C45" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="D45" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="E45">
         <v>2989</v>
@@ -4422,10 +4357,10 @@
         <v>45324.802951388891</v>
       </c>
       <c r="C46" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D46" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="E46">
         <v>3020</v>
@@ -4445,10 +4380,10 @@
         <v>45325.465196759258</v>
       </c>
       <c r="C47" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D47" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="E47">
         <v>2689</v>
@@ -4468,10 +4403,10 @@
         <v>45326.335520833331</v>
       </c>
       <c r="C48" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="D48" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="E48">
         <v>1759</v>
@@ -4491,10 +4426,10 @@
         <v>45326.494027777779</v>
       </c>
       <c r="C49" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="D49" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="E49">
         <v>2126</v>
@@ -4514,10 +4449,10 @@
         <v>45327.487939814811</v>
       </c>
       <c r="C50" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="D50" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="E50">
         <v>3064</v>
@@ -4537,10 +4472,10 @@
         <v>45328.373888888891</v>
       </c>
       <c r="C51" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D51" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="E51">
         <v>2530</v>
@@ -4560,10 +4495,10 @@
         <v>45328.773726851847</v>
       </c>
       <c r="C52" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="D52" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="E52">
         <v>2808</v>
@@ -4583,10 +4518,10 @@
         <v>45329.779687499999</v>
       </c>
       <c r="C53" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D53" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="E53">
         <v>2770</v>
@@ -4606,10 +4541,10 @@
         <v>45329.888101851851</v>
       </c>
       <c r="C54" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D54" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="E54">
         <v>3101</v>
@@ -4629,10 +4564,10 @@
         <v>45331.550879629627</v>
       </c>
       <c r="C55" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="D55" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="E55">
         <v>2475</v>
@@ -4652,10 +4587,10 @@
         <v>45331.960289351853</v>
       </c>
       <c r="C56" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="D56" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="E56">
         <v>2859</v>
@@ -4675,10 +4610,10 @@
         <v>45334.087071759262</v>
       </c>
       <c r="C57" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="D57" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E57">
         <v>3542</v>
@@ -4698,10 +4633,10 @@
         <v>45334.576053240737</v>
       </c>
       <c r="C58" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D58" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E58">
         <v>2292</v>
@@ -4721,10 +4656,10 @@
         <v>45334.825659722221</v>
       </c>
       <c r="C59" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="D59" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="E59">
         <v>3012</v>
@@ -4744,10 +4679,10 @@
         <v>45335.766898148147</v>
       </c>
       <c r="C60" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="D60" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="E60">
         <v>2681</v>
@@ -4767,10 +4702,10 @@
         <v>45335.925833333327</v>
       </c>
       <c r="C61" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D61" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="E61">
         <v>2393</v>
@@ -4790,10 +4725,10 @@
         <v>45336.444097222222</v>
       </c>
       <c r="C62" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="D62" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E62">
         <v>2489</v>
@@ -4813,10 +4748,10 @@
         <v>45337.486747685187</v>
       </c>
       <c r="C63" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="D63" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E63">
         <v>2720</v>
@@ -4836,10 +4771,10 @@
         <v>45338.904097222221</v>
       </c>
       <c r="C64" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="D64" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="E64">
         <v>2690</v>
@@ -4859,10 +4794,10 @@
         <v>45339.835787037038</v>
       </c>
       <c r="C65" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="D65" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="E65">
         <v>2667</v>
@@ -4882,10 +4817,10 @@
         <v>45340.472673611112</v>
       </c>
       <c r="C66" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D66" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="E66">
         <v>2904</v>
@@ -4905,10 +4840,10 @@
         <v>45342.400335648148</v>
       </c>
       <c r="C67" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D67" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E67">
         <v>4826</v>
@@ -4928,10 +4863,10 @@
         <v>45343.49858796296</v>
       </c>
       <c r="C68" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D68" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E68">
         <v>2904</v>
@@ -4951,10 +4886,10 @@
         <v>45343.889479166668</v>
       </c>
       <c r="C69" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="D69" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E69">
         <v>3237</v>
@@ -4974,10 +4909,10 @@
         <v>45345.104722222219</v>
       </c>
       <c r="C70" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D70" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E70">
         <v>2893</v>
@@ -4997,10 +4932,10 @@
         <v>45345.638506944437</v>
       </c>
       <c r="C71" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D71" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="E71">
         <v>3092</v>
@@ -5020,10 +4955,10 @@
         <v>45346.744976851849</v>
       </c>
       <c r="C72" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D72" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="E72">
         <v>2791</v>
@@ -5043,10 +4978,10 @@
         <v>45347.099062499998</v>
       </c>
       <c r="C73" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D73" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="E73">
         <v>2819</v>
@@ -5066,10 +5001,10 @@
         <v>45347.800509259258</v>
       </c>
       <c r="C74" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D74" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E74">
         <v>2531</v>
@@ -5089,10 +5024,10 @@
         <v>45348.80846064815</v>
       </c>
       <c r="C75" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D75" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E75">
         <v>3191</v>
@@ -5112,10 +5047,10 @@
         <v>45350.609340277777</v>
       </c>
       <c r="C76" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D76" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="E76">
         <v>2652</v>
@@ -5129,206 +5064,206 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>2129</v>
+        <v>2183</v>
       </c>
       <c r="B77" s="1">
-        <v>45352.532268518517</v>
+        <v>45354.905717592592</v>
       </c>
       <c r="C77" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D77" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E77">
-        <v>2557</v>
+        <v>2944</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>2131</v>
+        <v>2305</v>
       </c>
       <c r="B78" s="1">
-        <v>45352.636747685188</v>
+        <v>45364.008414351847</v>
       </c>
       <c r="C78" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D78" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="E78">
-        <v>2714</v>
+        <v>2413</v>
       </c>
       <c r="F78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>2166</v>
+        <v>2410</v>
       </c>
       <c r="B79" s="1">
-        <v>45354.356076388889</v>
+        <v>45370.409143518518</v>
       </c>
       <c r="C79" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D79" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E79">
-        <v>2629</v>
+        <v>3261</v>
       </c>
       <c r="F79">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G79">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>2183</v>
+        <v>2416</v>
       </c>
       <c r="B80" s="1">
-        <v>45354.905717592592</v>
+        <v>45370.621388888889</v>
       </c>
       <c r="C80" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D80" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E80">
-        <v>2944</v>
+        <v>2569</v>
       </c>
       <c r="F80">
+        <v>2</v>
+      </c>
+      <c r="G80">
         <v>1</v>
-      </c>
-      <c r="G80">
-        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>2223</v>
+        <v>2457</v>
       </c>
       <c r="B81" s="1">
-        <v>45358.309837962966</v>
+        <v>45372.773865740739</v>
       </c>
       <c r="C81" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D81" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E81">
-        <v>3206</v>
+        <v>2514</v>
       </c>
       <c r="F81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G81">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>2246</v>
+        <v>2470</v>
       </c>
       <c r="B82" s="1">
-        <v>45359.404594907413</v>
+        <v>45373.158703703702</v>
       </c>
       <c r="C82" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D82" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E82">
-        <v>3532</v>
+        <v>2787</v>
       </c>
       <c r="F82">
         <v>0</v>
       </c>
       <c r="G82">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>2263</v>
+        <v>2514</v>
       </c>
       <c r="B83" s="1">
-        <v>45360.635312500002</v>
+        <v>45375.100925925923</v>
       </c>
       <c r="C83" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D83" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E83">
-        <v>3219</v>
+        <v>2920</v>
       </c>
       <c r="F83">
         <v>0</v>
       </c>
       <c r="G83">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>2305</v>
+        <v>2539</v>
       </c>
       <c r="B84" s="1">
-        <v>45364.008414351847</v>
+        <v>45375.822152777779</v>
       </c>
       <c r="C84" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D84" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E84">
-        <v>2413</v>
+        <v>3245</v>
       </c>
       <c r="F84">
         <v>0</v>
       </c>
       <c r="G84">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>2329</v>
+        <v>2570</v>
       </c>
       <c r="B85" s="1">
-        <v>45364.823692129627</v>
+        <v>45377.716539351852</v>
       </c>
       <c r="C85" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D85" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E85">
-        <v>3375</v>
+        <v>2583</v>
       </c>
       <c r="F85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85">
         <v>3</v>
@@ -5336,364 +5271,364 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>2410</v>
+        <v>2595</v>
       </c>
       <c r="B86" s="1">
-        <v>45370.409143518518</v>
+        <v>45378.128032407411</v>
       </c>
       <c r="C86" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D86" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E86">
-        <v>3261</v>
+        <v>2203</v>
       </c>
       <c r="F86">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G86">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>2416</v>
+        <v>34</v>
       </c>
       <c r="B87" s="1">
-        <v>45370.621388888889</v>
-      </c>
-      <c r="C87" t="s">
-        <v>13</v>
+        <v>45285.891435185193</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="D87" t="s">
-        <v>12</v>
+        <v>174</v>
       </c>
       <c r="E87">
-        <v>2569</v>
+        <v>2930</v>
       </c>
       <c r="F87">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G87">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>2457</v>
+        <v>50</v>
       </c>
       <c r="B88" s="1">
-        <v>45372.773865740739</v>
-      </c>
-      <c r="C88" t="s">
-        <v>11</v>
+        <v>45286.058437500003</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>175</v>
       </c>
       <c r="D88" t="s">
-        <v>10</v>
+        <v>176</v>
       </c>
       <c r="E88">
-        <v>2514</v>
+        <v>3211</v>
       </c>
       <c r="F88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G88">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>2470</v>
+        <v>59</v>
       </c>
       <c r="B89" s="1">
-        <v>45373.158703703702</v>
-      </c>
-      <c r="C89" t="s">
-        <v>9</v>
+        <v>45286.466678240737</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>177</v>
       </c>
       <c r="D89" t="s">
-        <v>8</v>
+        <v>178</v>
       </c>
       <c r="E89">
-        <v>2787</v>
+        <v>3172</v>
       </c>
       <c r="F89">
         <v>0</v>
       </c>
       <c r="G89">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>2514</v>
+        <v>64</v>
       </c>
       <c r="B90" s="1">
-        <v>45375.100925925923</v>
-      </c>
-      <c r="C90" t="s">
+        <v>45286.474016203712</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D90" t="s">
+        <v>180</v>
+      </c>
+      <c r="E90">
+        <v>3445</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90">
         <v>7</v>
-      </c>
-      <c r="D90" t="s">
-        <v>6</v>
-      </c>
-      <c r="E90">
-        <v>2920</v>
-      </c>
-      <c r="F90">
-        <v>0</v>
-      </c>
-      <c r="G90">
-        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>2539</v>
+        <v>75</v>
       </c>
       <c r="B91" s="1">
-        <v>45375.822152777779</v>
-      </c>
-      <c r="C91" t="s">
-        <v>5</v>
+        <v>45286.841736111113</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>181</v>
       </c>
       <c r="D91" t="s">
-        <v>4</v>
+        <v>182</v>
       </c>
       <c r="E91">
-        <v>3245</v>
+        <v>3068</v>
       </c>
       <c r="F91">
         <v>0</v>
       </c>
       <c r="G91">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>2570</v>
+        <v>77</v>
       </c>
       <c r="B92" s="1">
-        <v>45377.716539351852</v>
-      </c>
-      <c r="C92" t="s">
-        <v>3</v>
+        <v>45286.890127314808</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="D92" t="s">
-        <v>2</v>
+        <v>184</v>
       </c>
       <c r="E92">
-        <v>2583</v>
+        <v>3007</v>
       </c>
       <c r="F92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>2595</v>
+        <v>78</v>
       </c>
       <c r="B93" s="1">
-        <v>45378.128032407411</v>
-      </c>
-      <c r="C93" t="s">
-        <v>1</v>
+        <v>45286.890381944453</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="D93" t="s">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="E93">
-        <v>2203</v>
+        <v>2903</v>
       </c>
       <c r="F93">
         <v>0</v>
       </c>
       <c r="G93">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="B94" s="1">
-        <v>45285.891435185193</v>
+        <v>45286.957361111112</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D94" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E94">
-        <v>2930</v>
+        <v>2939</v>
       </c>
       <c r="F94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="B95" s="1">
-        <v>45286.058437500003</v>
+        <v>45287.587824074071</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D95" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E95">
-        <v>3211</v>
+        <v>2998</v>
       </c>
       <c r="F95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G95">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="B96" s="1">
-        <v>45286.466678240737</v>
+        <v>45287.646481481483</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D96" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E96">
-        <v>3172</v>
+        <v>3198</v>
       </c>
       <c r="F96">
         <v>0</v>
       </c>
       <c r="G96">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>64</v>
+        <v>124</v>
       </c>
       <c r="B97" s="1">
-        <v>45286.474016203712</v>
+        <v>45287.759062500001</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D97" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E97">
-        <v>3445</v>
+        <v>3080</v>
       </c>
       <c r="F97">
         <v>0</v>
       </c>
       <c r="G97">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="B98" s="1">
-        <v>45286.841736111113</v>
+        <v>45287.777997685182</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D98" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E98">
-        <v>3068</v>
+        <v>3070</v>
       </c>
       <c r="F98">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G98">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="B99" s="1">
-        <v>45286.890127314808</v>
+        <v>45287.842245370368</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D99" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E99">
-        <v>3007</v>
+        <v>3292</v>
       </c>
       <c r="F99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>78</v>
+        <v>144</v>
       </c>
       <c r="B100" s="1">
-        <v>45286.890381944453</v>
+        <v>45288.060868055552</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D100" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E100">
-        <v>2903</v>
+        <v>3339</v>
       </c>
       <c r="F100">
         <v>0</v>
       </c>
       <c r="G100">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>83</v>
+        <v>152</v>
       </c>
       <c r="B101" s="1">
-        <v>45286.957361111112</v>
+        <v>45288.488645833328</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D101" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E101">
-        <v>2939</v>
+        <v>3177</v>
       </c>
       <c r="F101">
         <v>1</v>
@@ -5704,88 +5639,88 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="B102" s="1">
-        <v>45287.587824074071</v>
+        <v>45288.540763888886</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D102" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E102">
-        <v>2998</v>
+        <v>3217</v>
       </c>
       <c r="F102">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G102">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103">
-        <v>115</v>
+        <v>187</v>
       </c>
       <c r="B103" s="1">
-        <v>45287.646481481483</v>
+        <v>45289.451736111107</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D103" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E103">
-        <v>3198</v>
+        <v>3244</v>
       </c>
       <c r="F103">
         <v>0</v>
       </c>
       <c r="G103">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>124</v>
+        <v>204</v>
       </c>
       <c r="B104" s="1">
-        <v>45287.759062500001</v>
+        <v>45289.700659722221</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D104" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E104">
-        <v>3080</v>
+        <v>3554</v>
       </c>
       <c r="F104">
         <v>0</v>
       </c>
       <c r="G104">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>126</v>
+        <v>209</v>
       </c>
       <c r="B105" s="1">
-        <v>45287.777997685182</v>
+        <v>45289.762974537043</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D105" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E105">
-        <v>3070</v>
+        <v>3623</v>
       </c>
       <c r="F105">
         <v>2</v>
@@ -5796,137 +5731,137 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>135</v>
+        <v>222</v>
       </c>
       <c r="B106" s="1">
-        <v>45287.842245370368</v>
+        <v>45289.856805555559</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D106" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E106">
-        <v>3292</v>
+        <v>4213</v>
       </c>
       <c r="F106">
         <v>0</v>
       </c>
       <c r="G106">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107">
-        <v>144</v>
+        <v>238</v>
       </c>
       <c r="B107" s="1">
-        <v>45288.060868055552</v>
+        <v>45290.53570601852</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D107" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E107">
-        <v>3339</v>
+        <v>4048</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G107">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="B108" s="1">
-        <v>45288.488645833328</v>
+        <v>45290.988703703697</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D108" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E108">
-        <v>3177</v>
+        <v>3413</v>
       </c>
       <c r="F108">
         <v>1</v>
       </c>
       <c r="G108">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>153</v>
+        <v>265</v>
       </c>
       <c r="B109" s="1">
-        <v>45288.540763888886</v>
+        <v>45290.994062500002</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D109" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E109">
-        <v>3217</v>
+        <v>3409</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G109">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>187</v>
+        <v>272</v>
       </c>
       <c r="B110" s="1">
-        <v>45289.451736111107</v>
+        <v>45291.643425925933</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D110" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E110">
-        <v>3244</v>
+        <v>4258</v>
       </c>
       <c r="F110">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G110">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>204</v>
+        <v>280</v>
       </c>
       <c r="B111" s="1">
-        <v>45289.700659722221</v>
+        <v>45291.79519675926</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D111" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E111">
-        <v>3554</v>
+        <v>14809</v>
       </c>
       <c r="F111">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G111">
         <v>10</v>
@@ -5934,689 +5869,689 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>209</v>
+        <v>287</v>
       </c>
       <c r="B112" s="1">
-        <v>45289.762974537043</v>
+        <v>45292.275949074072</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D112" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E112">
-        <v>3623</v>
+        <v>4196</v>
       </c>
       <c r="F112">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G112">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113">
-        <v>222</v>
+        <v>292</v>
       </c>
       <c r="B113" s="1">
-        <v>45289.856805555559</v>
+        <v>45292.555636574078</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D113" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E113">
-        <v>4213</v>
+        <v>3847</v>
       </c>
       <c r="F113">
         <v>0</v>
       </c>
       <c r="G113">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114">
-        <v>238</v>
+        <v>310</v>
       </c>
       <c r="B114" s="1">
-        <v>45290.53570601852</v>
+        <v>45293.618275462963</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D114" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E114">
-        <v>4048</v>
+        <v>4109</v>
       </c>
       <c r="F114">
         <v>1</v>
       </c>
       <c r="G114">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>263</v>
+        <v>316</v>
       </c>
       <c r="B115" s="1">
-        <v>45290.988703703697</v>
+        <v>45293.993310185193</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D115" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E115">
-        <v>3413</v>
+        <v>3498</v>
       </c>
       <c r="F115">
         <v>1</v>
       </c>
       <c r="G115">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>265</v>
+        <v>318</v>
       </c>
       <c r="B116" s="1">
-        <v>45290.994062500002</v>
+        <v>45293.993981481479</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D116" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E116">
-        <v>3409</v>
+        <v>3286</v>
       </c>
       <c r="F116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G116">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117">
-        <v>272</v>
+        <v>325</v>
       </c>
       <c r="B117" s="1">
-        <v>45291.643425925933</v>
+        <v>45294.559259259258</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D117" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E117">
-        <v>4258</v>
+        <v>3677</v>
       </c>
       <c r="F117">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G117">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118">
-        <v>280</v>
+        <v>336</v>
       </c>
       <c r="B118" s="1">
-        <v>45291.79519675926</v>
+        <v>45294.860219907408</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D118" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E118">
-        <v>14809</v>
+        <v>3588</v>
       </c>
       <c r="F118">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G118">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119">
-        <v>287</v>
+        <v>338</v>
       </c>
       <c r="B119" s="1">
-        <v>45292.275949074072</v>
+        <v>45294.905069444438</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D119" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E119">
-        <v>4196</v>
+        <v>3507</v>
       </c>
       <c r="F119">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G119">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120">
-        <v>292</v>
+        <v>342</v>
       </c>
       <c r="B120" s="1">
-        <v>45292.555636574078</v>
+        <v>45294.91846064815</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D120" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E120">
-        <v>3847</v>
+        <v>3031</v>
       </c>
       <c r="F120">
         <v>0</v>
       </c>
       <c r="G120">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121">
-        <v>310</v>
+        <v>345</v>
       </c>
       <c r="B121" s="1">
-        <v>45293.618275462963</v>
+        <v>45294.934074074074</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D121" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E121">
-        <v>4109</v>
+        <v>3245</v>
       </c>
       <c r="F121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G121">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122">
-        <v>316</v>
+        <v>346</v>
       </c>
       <c r="B122" s="1">
-        <v>45293.993310185193</v>
+        <v>45294.939513888887</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D122" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E122">
-        <v>3498</v>
+        <v>3275</v>
       </c>
       <c r="F122">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123">
-        <v>318</v>
+        <v>361</v>
       </c>
       <c r="B123" s="1">
-        <v>45293.993981481479</v>
+        <v>45295.567719907413</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D123" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E123">
-        <v>3286</v>
+        <v>3277</v>
       </c>
       <c r="F123">
         <v>2</v>
       </c>
       <c r="G123">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124">
-        <v>325</v>
+        <v>400</v>
       </c>
       <c r="B124" s="1">
-        <v>45294.559259259258</v>
+        <v>45296.819224537037</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D124" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E124">
-        <v>3677</v>
+        <v>3257</v>
       </c>
       <c r="F124">
         <v>1</v>
       </c>
       <c r="G124">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125">
-        <v>336</v>
+        <v>410</v>
       </c>
       <c r="B125" s="1">
-        <v>45294.860219907408</v>
+        <v>45297.004004629627</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D125" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E125">
-        <v>3588</v>
+        <v>3184</v>
       </c>
       <c r="F125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G125">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126">
-        <v>338</v>
+        <v>417</v>
       </c>
       <c r="B126" s="1">
-        <v>45294.905069444438</v>
+        <v>45297.473668981482</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D126" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E126">
-        <v>3507</v>
+        <v>2820</v>
       </c>
       <c r="F126">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G126">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127">
-        <v>342</v>
+        <v>418</v>
       </c>
       <c r="B127" s="1">
-        <v>45294.91846064815</v>
+        <v>45297.481493055559</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D127" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E127">
-        <v>3031</v>
+        <v>2766</v>
       </c>
       <c r="F127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G127">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128">
-        <v>345</v>
+        <v>433</v>
       </c>
       <c r="B128" s="1">
-        <v>45294.934074074074</v>
+        <v>45297.601423611108</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D128" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E128">
-        <v>3245</v>
+        <v>2873</v>
       </c>
       <c r="F128">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G128">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129">
-        <v>346</v>
+        <v>435</v>
       </c>
       <c r="B129" s="1">
-        <v>45294.939513888887</v>
+        <v>45297.636874999997</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D129" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E129">
-        <v>3275</v>
+        <v>2789</v>
       </c>
       <c r="F129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G129">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130">
-        <v>361</v>
+        <v>440</v>
       </c>
       <c r="B130" s="1">
-        <v>45295.567719907413</v>
+        <v>45297.657187500001</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E130">
-        <v>3277</v>
+        <v>2835</v>
       </c>
       <c r="F130">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G130">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131">
-        <v>400</v>
+        <v>463</v>
       </c>
       <c r="B131" s="1">
-        <v>45296.819224537037</v>
+        <v>45298.045659722222</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D131" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E131">
-        <v>3257</v>
+        <v>3056</v>
       </c>
       <c r="F131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G131">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132">
-        <v>410</v>
+        <v>466</v>
       </c>
       <c r="B132" s="1">
-        <v>45297.004004629627</v>
+        <v>45298.328148148154</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D132" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E132">
-        <v>3184</v>
+        <v>3333</v>
       </c>
       <c r="F132">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G132">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133">
-        <v>417</v>
+        <v>468</v>
       </c>
       <c r="B133" s="1">
-        <v>45297.473668981482</v>
+        <v>45298.477430555547</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D133" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E133">
-        <v>2820</v>
+        <v>3225</v>
       </c>
       <c r="F133">
         <v>0</v>
       </c>
       <c r="G133">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134">
-        <v>418</v>
+        <v>474</v>
       </c>
       <c r="B134" s="1">
-        <v>45297.481493055559</v>
+        <v>45298.637604166674</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D134" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E134">
-        <v>2766</v>
+        <v>2831</v>
       </c>
       <c r="F134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G134">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135">
-        <v>433</v>
+        <v>478</v>
       </c>
       <c r="B135" s="1">
-        <v>45297.601423611108</v>
+        <v>45298.673298611109</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D135" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E135">
-        <v>2873</v>
+        <v>2940</v>
       </c>
       <c r="F135">
         <v>0</v>
       </c>
       <c r="G135">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136">
-        <v>435</v>
+        <v>493</v>
       </c>
       <c r="B136" s="1">
-        <v>45297.636874999997</v>
+        <v>45298.895231481481</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D136" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E136">
-        <v>2789</v>
+        <v>3284</v>
       </c>
       <c r="F136">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G136">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137">
-        <v>440</v>
+        <v>513</v>
       </c>
       <c r="B137" s="1">
-        <v>45297.657187500001</v>
+        <v>45299.761111111111</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D137" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E137">
-        <v>2835</v>
+        <v>3286</v>
       </c>
       <c r="F137">
         <v>0</v>
       </c>
       <c r="G137">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138">
-        <v>463</v>
+        <v>525</v>
       </c>
       <c r="B138" s="1">
-        <v>45298.045659722222</v>
+        <v>45300.110625000001</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D138" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E138">
-        <v>3056</v>
+        <v>3171</v>
       </c>
       <c r="F138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G138">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139">
-        <v>466</v>
+        <v>536</v>
       </c>
       <c r="B139" s="1">
-        <v>45298.328148148154</v>
+        <v>45300.624398148153</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D139" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E139">
-        <v>3333</v>
+        <v>2749</v>
       </c>
       <c r="F139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G139">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140">
-        <v>468</v>
+        <v>548</v>
       </c>
       <c r="B140" s="1">
-        <v>45298.477430555547</v>
+        <v>45300.848587962973</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D140" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E140">
-        <v>3225</v>
+        <v>2764</v>
       </c>
       <c r="F140">
         <v>0</v>
       </c>
       <c r="G140">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141">
-        <v>474</v>
+        <v>549</v>
       </c>
       <c r="B141" s="1">
-        <v>45298.637604166674</v>
+        <v>45300.848680555559</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D141" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E141">
-        <v>2831</v>
+        <v>2748</v>
       </c>
       <c r="F141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G141">
         <v>5</v>
@@ -6624,42 +6559,42 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142">
-        <v>478</v>
+        <v>555</v>
       </c>
       <c r="B142" s="1">
-        <v>45298.673298611109</v>
+        <v>45300.885520833333</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D142" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E142">
-        <v>2940</v>
+        <v>3015</v>
       </c>
       <c r="F142">
         <v>0</v>
       </c>
       <c r="G142">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143">
-        <v>493</v>
+        <v>556</v>
       </c>
       <c r="B143" s="1">
-        <v>45298.895231481481</v>
+        <v>45300.930266203701</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D143" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E143">
-        <v>3284</v>
+        <v>2805</v>
       </c>
       <c r="F143">
         <v>0</v>
@@ -6670,183 +6605,183 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144">
-        <v>513</v>
+        <v>566</v>
       </c>
       <c r="B144" s="1">
-        <v>45299.761111111111</v>
+        <v>45301.537106481483</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D144" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E144">
-        <v>3286</v>
+        <v>2974</v>
       </c>
       <c r="F144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G144">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145">
-        <v>525</v>
+        <v>568</v>
       </c>
       <c r="B145" s="1">
-        <v>45300.110625000001</v>
+        <v>45301.586527777778</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D145" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E145">
-        <v>3171</v>
+        <v>2913</v>
       </c>
       <c r="F145">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G145">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146">
-        <v>536</v>
+        <v>585</v>
       </c>
       <c r="B146" s="1">
-        <v>45300.624398148153</v>
+        <v>45301.887488425928</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D146" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E146">
-        <v>2749</v>
+        <v>3214</v>
       </c>
       <c r="F146">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G146">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147">
-        <v>548</v>
+        <v>593</v>
       </c>
       <c r="B147" s="1">
-        <v>45300.848587962973</v>
+        <v>45302.509953703702</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D147" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E147">
-        <v>2764</v>
+        <v>3288</v>
       </c>
       <c r="F147">
         <v>0</v>
       </c>
       <c r="G147">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148">
-        <v>549</v>
+        <v>602</v>
       </c>
       <c r="B148" s="1">
-        <v>45300.848680555559</v>
+        <v>45302.761250000003</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D148" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E148">
-        <v>2748</v>
+        <v>3186</v>
       </c>
       <c r="F148">
         <v>1</v>
       </c>
       <c r="G148">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149">
-        <v>555</v>
+        <v>623</v>
       </c>
       <c r="B149" s="1">
-        <v>45300.885520833333</v>
+        <v>45303.723900462966</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D149" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E149">
-        <v>3015</v>
+        <v>2791</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G149">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150">
-        <v>556</v>
+        <v>626</v>
       </c>
       <c r="B150" s="1">
-        <v>45300.930266203701</v>
+        <v>45303.777557870373</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D150" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E150">
-        <v>2805</v>
+        <v>2465</v>
       </c>
       <c r="F150">
         <v>0</v>
       </c>
       <c r="G150">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151">
-        <v>566</v>
+        <v>633</v>
       </c>
       <c r="B151" s="1">
-        <v>45301.537106481483</v>
+        <v>45303.86445601852</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D151" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E151">
-        <v>2974</v>
+        <v>2833</v>
       </c>
       <c r="F151">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G151">
         <v>6</v>
@@ -6854,735 +6789,735 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152">
-        <v>568</v>
+        <v>643</v>
       </c>
       <c r="B152" s="1">
-        <v>45301.586527777778</v>
+        <v>45304.817627314813</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D152" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E152">
-        <v>2913</v>
+        <v>2518</v>
       </c>
       <c r="F152">
         <v>0</v>
       </c>
       <c r="G152">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153">
-        <v>585</v>
+        <v>653</v>
       </c>
       <c r="B153" s="1">
-        <v>45301.887488425928</v>
+        <v>45305.017361111109</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D153" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E153">
-        <v>3214</v>
+        <v>2951</v>
       </c>
       <c r="F153">
         <v>1</v>
       </c>
       <c r="G153">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154">
-        <v>593</v>
+        <v>671</v>
       </c>
       <c r="B154" s="1">
-        <v>45302.509953703702</v>
+        <v>45306.008923611109</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D154" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E154">
-        <v>3288</v>
+        <v>2777</v>
       </c>
       <c r="F154">
         <v>0</v>
       </c>
       <c r="G154">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155">
-        <v>602</v>
+        <v>685</v>
       </c>
       <c r="B155" s="1">
-        <v>45302.761250000003</v>
+        <v>45306.985775462963</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D155" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E155">
-        <v>3186</v>
+        <v>3052</v>
       </c>
       <c r="F155">
         <v>1</v>
       </c>
       <c r="G155">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156">
-        <v>623</v>
+        <v>688</v>
       </c>
       <c r="B156" s="1">
-        <v>45303.723900462966</v>
+        <v>45307.012800925928</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D156" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E156">
-        <v>2791</v>
+        <v>3343</v>
       </c>
       <c r="F156">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G156">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157">
-        <v>626</v>
+        <v>691</v>
       </c>
       <c r="B157" s="1">
-        <v>45303.777557870373</v>
+        <v>45307.827777777777</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D157" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E157">
-        <v>2465</v>
+        <v>3495</v>
       </c>
       <c r="F157">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G157">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158">
-        <v>633</v>
+        <v>693</v>
       </c>
       <c r="B158" s="1">
-        <v>45303.86445601852</v>
+        <v>45307.9684375</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D158" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E158">
-        <v>2833</v>
+        <v>2944</v>
       </c>
       <c r="F158">
         <v>0</v>
       </c>
       <c r="G158">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159">
-        <v>643</v>
+        <v>699</v>
       </c>
       <c r="B159" s="1">
-        <v>45304.817627314813</v>
+        <v>45308.392060185193</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D159" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E159">
-        <v>2518</v>
+        <v>3065</v>
       </c>
       <c r="F159">
         <v>0</v>
       </c>
       <c r="G159">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160">
-        <v>653</v>
+        <v>717</v>
       </c>
       <c r="B160" s="1">
-        <v>45305.017361111109</v>
+        <v>45309.928171296298</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D160" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E160">
-        <v>2951</v>
+        <v>3271</v>
       </c>
       <c r="F160">
+        <v>0</v>
+      </c>
+      <c r="G160">
         <v>1</v>
-      </c>
-      <c r="G160">
-        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161">
-        <v>671</v>
+        <v>754</v>
       </c>
       <c r="B161" s="1">
-        <v>45306.008923611109</v>
+        <v>45312.30704861111</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D161" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E161">
-        <v>2777</v>
+        <v>2889</v>
       </c>
       <c r="F161">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G161">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162">
-        <v>685</v>
+        <v>755</v>
       </c>
       <c r="B162" s="1">
-        <v>45306.985775462963</v>
+        <v>45312.44630787037</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D162" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E162">
-        <v>3052</v>
+        <v>2768</v>
       </c>
       <c r="F162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G162">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163">
-        <v>688</v>
+        <v>767</v>
       </c>
       <c r="B163" s="1">
-        <v>45307.012800925928</v>
+        <v>45312.855381944442</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D163" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E163">
-        <v>3343</v>
+        <v>2453</v>
       </c>
       <c r="F163">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G163">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164">
-        <v>691</v>
+        <v>772</v>
       </c>
       <c r="B164" s="1">
-        <v>45307.827777777777</v>
+        <v>45312.865046296298</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D164" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E164">
-        <v>3495</v>
+        <v>2284</v>
       </c>
       <c r="F164">
         <v>1</v>
       </c>
       <c r="G164">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165">
-        <v>693</v>
+        <v>833</v>
       </c>
       <c r="B165" s="1">
-        <v>45307.9684375</v>
+        <v>45314.402499999997</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D165" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E165">
-        <v>2944</v>
+        <v>2652</v>
       </c>
       <c r="F165">
         <v>0</v>
       </c>
       <c r="G165">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166">
-        <v>699</v>
+        <v>844</v>
       </c>
       <c r="B166" s="1">
-        <v>45308.392060185193</v>
+        <v>45314.705752314818</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D166" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E166">
-        <v>3065</v>
+        <v>2220</v>
       </c>
       <c r="F166">
         <v>0</v>
       </c>
       <c r="G166">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167">
-        <v>717</v>
+        <v>861</v>
       </c>
       <c r="B167" s="1">
-        <v>45309.928171296298</v>
+        <v>45315.230543981481</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D167" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E167">
-        <v>3271</v>
+        <v>2713</v>
       </c>
       <c r="F167">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G167">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168">
-        <v>754</v>
+        <v>881</v>
       </c>
       <c r="B168" s="1">
-        <v>45312.30704861111</v>
+        <v>45315.729502314818</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D168" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E168">
-        <v>2889</v>
+        <v>2457</v>
       </c>
       <c r="F168">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G168">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169">
-        <v>755</v>
+        <v>903</v>
       </c>
       <c r="B169" s="1">
-        <v>45312.44630787037</v>
+        <v>45316.33421296296</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D169" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E169">
-        <v>2768</v>
+        <v>2322</v>
       </c>
       <c r="F169">
         <v>0</v>
       </c>
       <c r="G169">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170">
-        <v>767</v>
+        <v>904</v>
       </c>
       <c r="B170" s="1">
-        <v>45312.855381944442</v>
+        <v>45316.360185185193</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D170" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E170">
-        <v>2453</v>
+        <v>2537</v>
       </c>
       <c r="F170">
         <v>0</v>
       </c>
       <c r="G170">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171">
-        <v>772</v>
+        <v>908</v>
       </c>
       <c r="B171" s="1">
-        <v>45312.865046296298</v>
+        <v>45316.521458333344</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D171" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E171">
-        <v>2284</v>
+        <v>2432</v>
       </c>
       <c r="F171">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G171">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172">
-        <v>833</v>
+        <v>930</v>
       </c>
       <c r="B172" s="1">
-        <v>45314.402499999997</v>
+        <v>45316.911956018521</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D172" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E172">
-        <v>2652</v>
+        <v>2616</v>
       </c>
       <c r="F172">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G172">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173">
-        <v>844</v>
+        <v>934</v>
       </c>
       <c r="B173" s="1">
-        <v>45314.705752314818</v>
+        <v>45316.988425925927</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D173" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E173">
-        <v>2220</v>
+        <v>2703</v>
       </c>
       <c r="F173">
         <v>0</v>
       </c>
       <c r="G173">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174">
-        <v>861</v>
+        <v>935</v>
       </c>
       <c r="B174" s="1">
-        <v>45315.230543981481</v>
+        <v>45317.006990740738</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D174" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E174">
-        <v>2713</v>
+        <v>2440</v>
       </c>
       <c r="F174">
         <v>1</v>
       </c>
       <c r="G174">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175">
-        <v>881</v>
+        <v>969</v>
       </c>
       <c r="B175" s="1">
-        <v>45315.729502314818</v>
+        <v>45317.844467592593</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D175" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E175">
-        <v>2457</v>
+        <v>2364</v>
       </c>
       <c r="F175">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G175">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176">
-        <v>903</v>
+        <v>978</v>
       </c>
       <c r="B176" s="1">
-        <v>45316.33421296296</v>
+        <v>45318.345775462964</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D176" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E176">
-        <v>2322</v>
+        <v>2496</v>
       </c>
       <c r="F176">
         <v>0</v>
       </c>
       <c r="G176">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177">
-        <v>904</v>
+        <v>979</v>
       </c>
       <c r="B177" s="1">
-        <v>45316.360185185193</v>
+        <v>45318.346388888887</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D177" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E177">
-        <v>2537</v>
+        <v>2438</v>
       </c>
       <c r="F177">
         <v>0</v>
       </c>
       <c r="G177">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178">
-        <v>908</v>
+        <v>990</v>
       </c>
       <c r="B178" s="1">
-        <v>45316.521458333344</v>
+        <v>45318.454594907409</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D178" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E178">
-        <v>2432</v>
+        <v>2108</v>
       </c>
       <c r="F178">
         <v>0</v>
       </c>
       <c r="G178">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179">
-        <v>930</v>
+        <v>992</v>
       </c>
       <c r="B179" s="1">
-        <v>45316.911956018521</v>
+        <v>45318.467476851853</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D179" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E179">
-        <v>2616</v>
+        <v>2057</v>
       </c>
       <c r="F179">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G179">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180">
-        <v>934</v>
+        <v>1004</v>
       </c>
       <c r="B180" s="1">
-        <v>45316.988425925927</v>
+        <v>45318.64266203704</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D180" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E180">
-        <v>2703</v>
+        <v>2202</v>
       </c>
       <c r="F180">
         <v>0</v>
       </c>
       <c r="G180">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181">
-        <v>935</v>
+        <v>1007</v>
       </c>
       <c r="B181" s="1">
-        <v>45317.006990740738</v>
+        <v>45318.714594907397</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D181" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E181">
-        <v>2440</v>
+        <v>2033</v>
       </c>
       <c r="F181">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G181">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182">
-        <v>969</v>
+        <v>1020</v>
       </c>
       <c r="B182" s="1">
-        <v>45317.844467592593</v>
+        <v>45318.777673611112</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D182" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E182">
-        <v>2364</v>
+        <v>2018</v>
       </c>
       <c r="F182">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G182">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183">
-        <v>978</v>
+        <v>1047</v>
       </c>
       <c r="B183" s="1">
-        <v>45318.345775462964</v>
+        <v>45319.373796296299</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D183" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E183">
-        <v>2496</v>
+        <v>2183</v>
       </c>
       <c r="F183">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G183">
         <v>3</v>
@@ -7590,171 +7525,171 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184">
-        <v>979</v>
+        <v>1053</v>
       </c>
       <c r="B184" s="1">
-        <v>45318.346388888887</v>
+        <v>45319.468414351853</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D184" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E184">
-        <v>2438</v>
+        <v>2140</v>
       </c>
       <c r="F184">
         <v>0</v>
       </c>
       <c r="G184">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185">
-        <v>990</v>
+        <v>1062</v>
       </c>
       <c r="B185" s="1">
-        <v>45318.454594907409</v>
+        <v>45319.735486111109</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D185" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E185">
-        <v>2108</v>
+        <v>2502</v>
       </c>
       <c r="F185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G185">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186">
-        <v>992</v>
+        <v>1103</v>
       </c>
       <c r="B186" s="1">
-        <v>45318.467476851853</v>
+        <v>45320.771863425929</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D186" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E186">
-        <v>2057</v>
+        <v>2198</v>
       </c>
       <c r="F186">
         <v>0</v>
       </c>
       <c r="G186">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187">
-        <v>1004</v>
+        <v>1120</v>
       </c>
       <c r="B187" s="1">
-        <v>45318.64266203704</v>
+        <v>45320.964849537027</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D187" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E187">
-        <v>2202</v>
+        <v>2745</v>
       </c>
       <c r="F187">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G187">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188">
-        <v>1007</v>
+        <v>1122</v>
       </c>
       <c r="B188" s="1">
-        <v>45318.714594907397</v>
+        <v>45321.237291666657</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D188" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E188">
-        <v>2033</v>
+        <v>2596</v>
       </c>
       <c r="F188">
         <v>0</v>
       </c>
       <c r="G188">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189">
-        <v>1020</v>
+        <v>1173</v>
       </c>
       <c r="B189" s="1">
-        <v>45318.777673611112</v>
+        <v>45322.697847222233</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D189" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E189">
-        <v>2018</v>
+        <v>2821</v>
       </c>
       <c r="F189">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G189">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190">
-        <v>1047</v>
+        <v>1187</v>
       </c>
       <c r="B190" s="1">
-        <v>45319.373796296299</v>
+        <v>45323.416875000003</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D190" t="s">
         <v>379</v>
       </c>
       <c r="E190">
-        <v>2183</v>
+        <v>2809</v>
       </c>
       <c r="F190">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G190">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191">
-        <v>1053</v>
+        <v>1192</v>
       </c>
       <c r="B191" s="1">
-        <v>45319.468414351853</v>
+        <v>45323.581250000003</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>380</v>
@@ -7763,21 +7698,21 @@
         <v>381</v>
       </c>
       <c r="E191">
-        <v>2140</v>
+        <v>2912</v>
       </c>
       <c r="F191">
         <v>0</v>
       </c>
       <c r="G191">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192">
-        <v>1062</v>
+        <v>1200</v>
       </c>
       <c r="B192" s="1">
-        <v>45319.735486111109</v>
+        <v>45323.833483796298</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>382</v>
@@ -7786,21 +7721,21 @@
         <v>383</v>
       </c>
       <c r="E192">
-        <v>2502</v>
+        <v>2837</v>
       </c>
       <c r="F192">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G192">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193">
-        <v>1103</v>
+        <v>1217</v>
       </c>
       <c r="B193" s="1">
-        <v>45320.771863425929</v>
+        <v>45324.132962962962</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>384</v>
@@ -7809,21 +7744,21 @@
         <v>385</v>
       </c>
       <c r="E193">
-        <v>2198</v>
+        <v>2469</v>
       </c>
       <c r="F193">
         <v>0</v>
       </c>
       <c r="G193">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194">
-        <v>1120</v>
+        <v>1230</v>
       </c>
       <c r="B194" s="1">
-        <v>45320.964849537027</v>
+        <v>45324.392824074072</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>386</v>
@@ -7832,21 +7767,21 @@
         <v>387</v>
       </c>
       <c r="E194">
-        <v>2745</v>
+        <v>2781</v>
       </c>
       <c r="F194">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G194">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195">
-        <v>1122</v>
+        <v>1231</v>
       </c>
       <c r="B195" s="1">
-        <v>45321.237291666657</v>
+        <v>45324.397685185177</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>388</v>
@@ -7855,21 +7790,21 @@
         <v>389</v>
       </c>
       <c r="E195">
-        <v>2596</v>
+        <v>2786</v>
       </c>
       <c r="F195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G195">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196">
-        <v>1173</v>
+        <v>1256</v>
       </c>
       <c r="B196" s="1">
-        <v>45322.697847222233</v>
+        <v>45325.430543981478</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>390</v>
@@ -7878,10 +7813,10 @@
         <v>391</v>
       </c>
       <c r="E196">
-        <v>2821</v>
+        <v>2174</v>
       </c>
       <c r="F196">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G196">
         <v>5</v>
@@ -7889,295 +7824,295 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197">
-        <v>1187</v>
+        <v>1267</v>
       </c>
       <c r="B197" s="1">
-        <v>45323.416875000003</v>
+        <v>45325.515775462962</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>392</v>
       </c>
       <c r="D197" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E197">
-        <v>2809</v>
+        <v>2687</v>
       </c>
       <c r="F197">
         <v>0</v>
       </c>
       <c r="G197">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198">
-        <v>1192</v>
+        <v>1285</v>
       </c>
       <c r="B198" s="1">
-        <v>45323.581250000003</v>
+        <v>45326.31863425926</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D198" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E198">
-        <v>2912</v>
+        <v>3165</v>
       </c>
       <c r="F198">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G198">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199">
-        <v>1200</v>
+        <v>1385</v>
       </c>
       <c r="B199" s="1">
-        <v>45323.833483796298</v>
+        <v>45328.40697916667</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D199" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E199">
-        <v>2837</v>
+        <v>2520</v>
       </c>
       <c r="F199">
         <v>0</v>
       </c>
       <c r="G199">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200">
-        <v>1217</v>
+        <v>1388</v>
       </c>
       <c r="B200" s="1">
-        <v>45324.132962962962</v>
+        <v>45328.551354166673</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D200" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E200">
-        <v>2469</v>
+        <v>2547</v>
       </c>
       <c r="F200">
         <v>0</v>
       </c>
       <c r="G200">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201">
-        <v>1230</v>
+        <v>1389</v>
       </c>
       <c r="B201" s="1">
-        <v>45324.392824074072</v>
+        <v>45328.594641203701</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D201" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E201">
-        <v>2781</v>
+        <v>2631</v>
       </c>
       <c r="F201">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G201">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202">
-        <v>1231</v>
+        <v>1415</v>
       </c>
       <c r="B202" s="1">
-        <v>45324.397685185177</v>
+        <v>45329.43849537037</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D202" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E202">
-        <v>2786</v>
+        <v>2291</v>
       </c>
       <c r="F202">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G202">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203">
-        <v>1256</v>
+        <v>1419</v>
       </c>
       <c r="B203" s="1">
-        <v>45325.430543981478</v>
+        <v>45329.504652777781</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D203" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E203">
-        <v>2174</v>
+        <v>2750</v>
       </c>
       <c r="F203">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G203">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204">
-        <v>1267</v>
+        <v>1430</v>
       </c>
       <c r="B204" s="1">
-        <v>45325.515775462962</v>
+        <v>45329.7658912037</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D204" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E204">
-        <v>2687</v>
+        <v>2480</v>
       </c>
       <c r="F204">
         <v>0</v>
       </c>
       <c r="G204">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205">
-        <v>1285</v>
+        <v>1435</v>
       </c>
       <c r="B205" s="1">
-        <v>45326.31863425926</v>
+        <v>45329.845104166663</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D205" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E205">
-        <v>3165</v>
+        <v>2550</v>
       </c>
       <c r="F205">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G205">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206">
-        <v>1385</v>
+        <v>1452</v>
       </c>
       <c r="B206" s="1">
-        <v>45328.40697916667</v>
+        <v>45330.353726851848</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D206" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E206">
-        <v>2520</v>
+        <v>3179</v>
       </c>
       <c r="F206">
         <v>0</v>
       </c>
       <c r="G206">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207">
-        <v>1388</v>
+        <v>1458</v>
       </c>
       <c r="B207" s="1">
-        <v>45328.551354166673</v>
+        <v>45330.645243055558</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D207" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E207">
-        <v>2547</v>
+        <v>3273</v>
       </c>
       <c r="F207">
         <v>0</v>
       </c>
       <c r="G207">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208">
-        <v>1389</v>
+        <v>1473</v>
       </c>
       <c r="B208" s="1">
-        <v>45328.594641203701</v>
+        <v>45331.435300925928</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D208" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E208">
-        <v>2631</v>
+        <v>3438</v>
       </c>
       <c r="F208">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G208">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209">
-        <v>1415</v>
+        <v>1479</v>
       </c>
       <c r="B209" s="1">
-        <v>45329.43849537037</v>
+        <v>45331.538344907407</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D209" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E209">
-        <v>2291</v>
+        <v>2272</v>
       </c>
       <c r="F209">
         <v>0</v>
@@ -8188,33 +8123,33 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210">
-        <v>1419</v>
+        <v>1508</v>
       </c>
       <c r="B210" s="1">
-        <v>45329.504652777781</v>
+        <v>45331.90834490741</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D210" t="s">
         <v>418</v>
       </c>
       <c r="E210">
-        <v>2750</v>
+        <v>2706</v>
       </c>
       <c r="F210">
+        <v>1</v>
+      </c>
+      <c r="G210">
         <v>3</v>
-      </c>
-      <c r="G210">
-        <v>4</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211">
-        <v>1430</v>
+        <v>1520</v>
       </c>
       <c r="B211" s="1">
-        <v>45329.7658912037</v>
+        <v>45332.581597222219</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>419</v>
@@ -8223,21 +8158,21 @@
         <v>420</v>
       </c>
       <c r="E211">
-        <v>2480</v>
+        <v>2814</v>
       </c>
       <c r="F211">
         <v>0</v>
       </c>
       <c r="G211">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212">
-        <v>1435</v>
+        <v>1531</v>
       </c>
       <c r="B212" s="1">
-        <v>45329.845104166663</v>
+        <v>45332.775254629632</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>421</v>
@@ -8246,21 +8181,21 @@
         <v>422</v>
       </c>
       <c r="E212">
-        <v>2550</v>
+        <v>2562</v>
       </c>
       <c r="F212">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G212">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213">
-        <v>1452</v>
+        <v>1536</v>
       </c>
       <c r="B213" s="1">
-        <v>45330.353726851848</v>
+        <v>45332.878472222219</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>423</v>
@@ -8269,21 +8204,21 @@
         <v>424</v>
       </c>
       <c r="E213">
-        <v>3179</v>
+        <v>2522</v>
       </c>
       <c r="F213">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G213">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214">
-        <v>1458</v>
+        <v>1548</v>
       </c>
       <c r="B214" s="1">
-        <v>45330.645243055558</v>
+        <v>45333.481747685182</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>425</v>
@@ -8292,7 +8227,7 @@
         <v>426</v>
       </c>
       <c r="E214">
-        <v>3273</v>
+        <v>2587</v>
       </c>
       <c r="F214">
         <v>0</v>
@@ -8303,10 +8238,10 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215">
-        <v>1473</v>
+        <v>1554</v>
       </c>
       <c r="B215" s="1">
-        <v>45331.435300925928</v>
+        <v>45333.614120370366</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>427</v>
@@ -8315,21 +8250,21 @@
         <v>428</v>
       </c>
       <c r="E215">
-        <v>3438</v>
+        <v>2232</v>
       </c>
       <c r="F215">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G215">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216">
-        <v>1479</v>
+        <v>1566</v>
       </c>
       <c r="B216" s="1">
-        <v>45331.538344907407</v>
+        <v>45333.746851851851</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>429</v>
@@ -8338,102 +8273,102 @@
         <v>430</v>
       </c>
       <c r="E216">
-        <v>2272</v>
+        <v>3121</v>
       </c>
       <c r="F216">
         <v>0</v>
       </c>
       <c r="G216">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217">
-        <v>1508</v>
+        <v>1570</v>
       </c>
       <c r="B217" s="1">
-        <v>45331.90834490741</v>
+        <v>45333.861562500002</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>431</v>
       </c>
       <c r="D217" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E217">
-        <v>2706</v>
+        <v>3153</v>
       </c>
       <c r="F217">
         <v>1</v>
       </c>
       <c r="G217">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218">
-        <v>1520</v>
+        <v>1586</v>
       </c>
       <c r="B218" s="1">
-        <v>45332.581597222219</v>
+        <v>45334.575486111113</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D218" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E218">
-        <v>2814</v>
+        <v>2331</v>
       </c>
       <c r="F218">
         <v>0</v>
       </c>
       <c r="G218">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219">
-        <v>1531</v>
+        <v>1603</v>
       </c>
       <c r="B219" s="1">
-        <v>45332.775254629632</v>
+        <v>45334.695370370369</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D219" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E219">
-        <v>2562</v>
+        <v>2383</v>
       </c>
       <c r="F219">
         <v>1</v>
       </c>
       <c r="G219">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220">
-        <v>1536</v>
+        <v>1604</v>
       </c>
       <c r="B220" s="1">
-        <v>45332.878472222219</v>
+        <v>45334.699247685188</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D220" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E220">
-        <v>2522</v>
+        <v>2651</v>
       </c>
       <c r="F220">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G220">
         <v>6</v>
@@ -8441,631 +8376,631 @@
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221">
-        <v>1548</v>
+        <v>1610</v>
       </c>
       <c r="B221" s="1">
-        <v>45333.481747685182</v>
+        <v>45334.792245370372</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D221" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E221">
-        <v>2587</v>
+        <v>2774</v>
       </c>
       <c r="F221">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G221">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222">
-        <v>1554</v>
+        <v>1617</v>
       </c>
       <c r="B222" s="1">
-        <v>45333.614120370366</v>
+        <v>45335.007951388892</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D222" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E222">
-        <v>2232</v>
+        <v>3524</v>
       </c>
       <c r="F222">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G222">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223">
-        <v>1566</v>
+        <v>1623</v>
       </c>
       <c r="B223" s="1">
-        <v>45333.746851851851</v>
+        <v>45335.605856481481</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D223" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E223">
-        <v>3121</v>
+        <v>2773</v>
       </c>
       <c r="F223">
         <v>0</v>
       </c>
       <c r="G223">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224">
-        <v>1570</v>
+        <v>1626</v>
       </c>
       <c r="B224" s="1">
-        <v>45333.861562500002</v>
+        <v>45335.696446759262</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D224" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E224">
-        <v>3153</v>
+        <v>2992</v>
       </c>
       <c r="F224">
+        <v>0</v>
+      </c>
+      <c r="G224">
         <v>1</v>
-      </c>
-      <c r="G224">
-        <v>9</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225">
-        <v>1586</v>
+        <v>1633</v>
       </c>
       <c r="B225" s="1">
-        <v>45334.575486111113</v>
+        <v>45335.767534722218</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D225" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E225">
-        <v>2331</v>
+        <v>2696</v>
       </c>
       <c r="F225">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G225">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226">
-        <v>1603</v>
+        <v>1635</v>
       </c>
       <c r="B226" s="1">
-        <v>45334.695370370369</v>
+        <v>45335.779467592591</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D226" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E226">
-        <v>2383</v>
+        <v>2841</v>
       </c>
       <c r="F226">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G226">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227">
-        <v>1604</v>
+        <v>1636</v>
       </c>
       <c r="B227" s="1">
-        <v>45334.699247685188</v>
+        <v>45335.780219907407</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D227" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E227">
-        <v>2651</v>
+        <v>2514</v>
       </c>
       <c r="F227">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G227">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228">
-        <v>1610</v>
+        <v>1641</v>
       </c>
       <c r="B228" s="1">
-        <v>45334.792245370372</v>
+        <v>45335.80877314815</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D228" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E228">
-        <v>2774</v>
+        <v>2309</v>
       </c>
       <c r="F228">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G228">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229">
-        <v>1617</v>
+        <v>1644</v>
       </c>
       <c r="B229" s="1">
-        <v>45335.007951388892</v>
+        <v>45335.812175925923</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D229" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E229">
-        <v>3524</v>
+        <v>2086</v>
       </c>
       <c r="F229">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G229">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230">
-        <v>1623</v>
+        <v>1673</v>
       </c>
       <c r="B230" s="1">
-        <v>45335.605856481481</v>
+        <v>45336.359895833331</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D230" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E230">
-        <v>2773</v>
+        <v>2756</v>
       </c>
       <c r="F230">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G230">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231">
-        <v>1626</v>
+        <v>1683</v>
       </c>
       <c r="B231" s="1">
-        <v>45335.696446759262</v>
+        <v>45336.428657407407</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D231" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E231">
-        <v>2992</v>
+        <v>2122</v>
       </c>
       <c r="F231">
         <v>0</v>
       </c>
       <c r="G231">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232">
-        <v>1633</v>
+        <v>1684</v>
       </c>
       <c r="B232" s="1">
-        <v>45335.767534722218</v>
+        <v>45336.429212962961</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D232" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E232">
-        <v>2696</v>
+        <v>2256</v>
       </c>
       <c r="F232">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G232">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233">
-        <v>1635</v>
+        <v>1691</v>
       </c>
       <c r="B233" s="1">
-        <v>45335.779467592591</v>
+        <v>45336.535578703697</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D233" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E233">
-        <v>2841</v>
+        <v>2770</v>
       </c>
       <c r="F233">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G233">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234">
-        <v>1636</v>
+        <v>1720</v>
       </c>
       <c r="B234" s="1">
-        <v>45335.780219907407</v>
+        <v>45337.666863425933</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D234" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E234">
-        <v>2514</v>
+        <v>3309</v>
       </c>
       <c r="F234">
         <v>0</v>
       </c>
       <c r="G234">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235">
-        <v>1641</v>
+        <v>1721</v>
       </c>
       <c r="B235" s="1">
-        <v>45335.80877314815</v>
+        <v>45337.723587962973</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D235" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E235">
-        <v>2309</v>
+        <v>3274</v>
       </c>
       <c r="F235">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G235">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236">
-        <v>1644</v>
+        <v>1747</v>
       </c>
       <c r="B236" s="1">
-        <v>45335.812175925923</v>
+        <v>45338.884016203701</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D236" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E236">
-        <v>2086</v>
+        <v>3097</v>
       </c>
       <c r="F236">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G236">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237">
-        <v>1673</v>
+        <v>1762</v>
       </c>
       <c r="B237" s="1">
-        <v>45336.359895833331</v>
+        <v>45339.374236111107</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D237" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E237">
-        <v>2756</v>
+        <v>2770</v>
       </c>
       <c r="F237">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G237">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238">
-        <v>1683</v>
+        <v>1773</v>
       </c>
       <c r="B238" s="1">
-        <v>45336.428657407407</v>
+        <v>45339.687048611107</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D238" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E238">
-        <v>2122</v>
+        <v>2438</v>
       </c>
       <c r="F238">
         <v>0</v>
       </c>
       <c r="G238">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239">
-        <v>1684</v>
+        <v>1817</v>
       </c>
       <c r="B239" s="1">
-        <v>45336.429212962961</v>
+        <v>45341.453518518523</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D239" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E239">
-        <v>2256</v>
+        <v>2733</v>
       </c>
       <c r="F239">
         <v>0</v>
       </c>
       <c r="G239">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240">
-        <v>1691</v>
+        <v>1821</v>
       </c>
       <c r="B240" s="1">
-        <v>45336.535578703697</v>
+        <v>45341.577604166669</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D240" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E240">
-        <v>2770</v>
+        <v>3307</v>
       </c>
       <c r="F240">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G240">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241">
-        <v>1720</v>
+        <v>1864</v>
       </c>
       <c r="B241" s="1">
-        <v>45337.666863425933</v>
+        <v>45342.793553240743</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D241" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E241">
-        <v>3309</v>
+        <v>3174</v>
       </c>
       <c r="F241">
         <v>0</v>
       </c>
       <c r="G241">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242">
-        <v>1721</v>
+        <v>1885</v>
       </c>
       <c r="B242" s="1">
-        <v>45337.723587962973</v>
+        <v>45343.640960648147</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D242" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E242">
-        <v>3274</v>
+        <v>3092</v>
       </c>
       <c r="F242">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G242">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243">
-        <v>1747</v>
+        <v>1888</v>
       </c>
       <c r="B243" s="1">
-        <v>45338.884016203701</v>
+        <v>45343.827106481483</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D243" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E243">
-        <v>3097</v>
+        <v>3095</v>
       </c>
       <c r="F243">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G243">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244">
-        <v>1762</v>
+        <v>1889</v>
       </c>
       <c r="B244" s="1">
-        <v>45339.374236111107</v>
+        <v>45343.843113425923</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D244" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E244">
-        <v>2770</v>
+        <v>3409</v>
       </c>
       <c r="F244">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G244">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245">
-        <v>1773</v>
+        <v>1898</v>
       </c>
       <c r="B245" s="1">
-        <v>45339.687048611107</v>
+        <v>45344.319085648152</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D245" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E245">
-        <v>2438</v>
+        <v>3674</v>
       </c>
       <c r="F245">
         <v>0</v>
       </c>
       <c r="G245">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246">
-        <v>1807</v>
+        <v>1901</v>
       </c>
       <c r="B246" s="1">
-        <v>45340.803784722222</v>
+        <v>45344.46429398148</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D246" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E246">
-        <v>3105</v>
+        <v>3069</v>
       </c>
       <c r="F246">
         <v>0</v>
       </c>
       <c r="G246">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247">
-        <v>1817</v>
+        <v>1916</v>
       </c>
       <c r="B247" s="1">
-        <v>45341.453518518523</v>
+        <v>45344.819293981483</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D247" t="s">
         <v>491</v>
       </c>
       <c r="E247">
-        <v>2733</v>
+        <v>2825</v>
       </c>
       <c r="F247">
         <v>0</v>
       </c>
       <c r="G247">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248">
-        <v>1821</v>
+        <v>1917</v>
       </c>
       <c r="B248" s="1">
-        <v>45341.577604166669</v>
+        <v>45344.874074074083</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>492</v>
@@ -9074,21 +9009,21 @@
         <v>493</v>
       </c>
       <c r="E248">
-        <v>3307</v>
+        <v>3029</v>
       </c>
       <c r="F248">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G248">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249">
-        <v>1864</v>
+        <v>1935</v>
       </c>
       <c r="B249" s="1">
-        <v>45342.793553240743</v>
+        <v>45345.634120370371</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>494</v>
@@ -9097,21 +9032,21 @@
         <v>495</v>
       </c>
       <c r="E249">
-        <v>3174</v>
+        <v>3002</v>
       </c>
       <c r="F249">
         <v>0</v>
       </c>
       <c r="G249">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250">
-        <v>1885</v>
+        <v>1945</v>
       </c>
       <c r="B250" s="1">
-        <v>45343.640960648147</v>
+        <v>45345.778923611113</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>496</v>
@@ -9120,21 +9055,21 @@
         <v>497</v>
       </c>
       <c r="E250">
-        <v>3092</v>
+        <v>2801</v>
       </c>
       <c r="F250">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G250">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251">
-        <v>1888</v>
+        <v>1948</v>
       </c>
       <c r="B251" s="1">
-        <v>45343.827106481483</v>
+        <v>45345.858958333331</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>498</v>
@@ -9143,21 +9078,21 @@
         <v>499</v>
       </c>
       <c r="E251">
-        <v>3095</v>
+        <v>3029</v>
       </c>
       <c r="F251">
         <v>0</v>
       </c>
       <c r="G251">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252">
-        <v>1889</v>
+        <v>1961</v>
       </c>
       <c r="B252" s="1">
-        <v>45343.843113425923</v>
+        <v>45346.495081018518</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>500</v>
@@ -9166,21 +9101,21 @@
         <v>501</v>
       </c>
       <c r="E252">
-        <v>3409</v>
+        <v>2437</v>
       </c>
       <c r="F252">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G252">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253">
-        <v>1898</v>
+        <v>1967</v>
       </c>
       <c r="B253" s="1">
-        <v>45344.319085648152</v>
+        <v>45346.620682870373</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>502</v>
@@ -9189,21 +9124,21 @@
         <v>503</v>
       </c>
       <c r="E253">
-        <v>3674</v>
+        <v>2641</v>
       </c>
       <c r="F253">
         <v>0</v>
       </c>
       <c r="G253">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254">
-        <v>1901</v>
+        <v>1993</v>
       </c>
       <c r="B254" s="1">
-        <v>45344.46429398148</v>
+        <v>45347.378819444442</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>504</v>
@@ -9212,7 +9147,7 @@
         <v>505</v>
       </c>
       <c r="E254">
-        <v>3069</v>
+        <v>2260</v>
       </c>
       <c r="F254">
         <v>0</v>
@@ -9223,677 +9158,677 @@
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255">
-        <v>1916</v>
+        <v>1999</v>
       </c>
       <c r="B255" s="1">
-        <v>45344.819293981483</v>
+        <v>45347.535532407397</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>506</v>
       </c>
       <c r="D255" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E255">
-        <v>2825</v>
+        <v>2281</v>
       </c>
       <c r="F255">
         <v>0</v>
       </c>
       <c r="G255">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256">
-        <v>1917</v>
+        <v>2012</v>
       </c>
       <c r="B256" s="1">
-        <v>45344.874074074083</v>
+        <v>45347.662129629629</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D256" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E256">
-        <v>3029</v>
+        <v>2327</v>
       </c>
       <c r="F256">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G256">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A257">
-        <v>1935</v>
+        <v>2027</v>
       </c>
       <c r="B257" s="1">
-        <v>45345.634120370371</v>
+        <v>45348.001400462963</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D257" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E257">
-        <v>3002</v>
+        <v>2409</v>
       </c>
       <c r="F257">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G257">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A258">
-        <v>1945</v>
+        <v>2064</v>
       </c>
       <c r="B258" s="1">
-        <v>45345.778923611113</v>
+        <v>45349.484930555547</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D258" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E258">
-        <v>2801</v>
+        <v>3215</v>
       </c>
       <c r="F258">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G258">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A259">
-        <v>1948</v>
+        <v>2074</v>
       </c>
       <c r="B259" s="1">
-        <v>45345.858958333331</v>
+        <v>45349.776145833333</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D259" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E259">
-        <v>3029</v>
+        <v>2830</v>
       </c>
       <c r="F259">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G259">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A260">
-        <v>1961</v>
+        <v>2083</v>
       </c>
       <c r="B260" s="1">
-        <v>45346.495081018518</v>
+        <v>45350.384687500002</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D260" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E260">
-        <v>2437</v>
+        <v>2846</v>
       </c>
       <c r="F260">
         <v>0</v>
       </c>
       <c r="G260">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A261">
-        <v>1967</v>
+        <v>2135</v>
       </c>
       <c r="B261" s="1">
-        <v>45346.620682870373</v>
+        <v>45352.732627314806</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D261" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E261">
-        <v>2641</v>
+        <v>2833</v>
       </c>
       <c r="F261">
         <v>0</v>
       </c>
       <c r="G261">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A262">
-        <v>1993</v>
+        <v>2198</v>
       </c>
       <c r="B262" s="1">
-        <v>45347.378819444442</v>
+        <v>45356.725115740737</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D262" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E262">
-        <v>2260</v>
+        <v>3475</v>
       </c>
       <c r="F262">
         <v>0</v>
       </c>
       <c r="G262">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A263">
-        <v>1999</v>
+        <v>2213</v>
       </c>
       <c r="B263" s="1">
-        <v>45347.535532407397</v>
+        <v>45357.559155092589</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D263" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E263">
-        <v>2281</v>
+        <v>2836</v>
       </c>
       <c r="F263">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G263">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A264">
-        <v>2012</v>
+        <v>2248</v>
       </c>
       <c r="B264" s="1">
-        <v>45347.662129629629</v>
+        <v>45359.527303240742</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D264" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E264">
-        <v>2327</v>
+        <v>3010</v>
       </c>
       <c r="F264">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G264">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A265">
-        <v>2027</v>
+        <v>2271</v>
       </c>
       <c r="B265" s="1">
-        <v>45348.001400462963</v>
+        <v>45361.71707175926</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D265" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E265">
-        <v>2409</v>
+        <v>3341</v>
       </c>
       <c r="F265">
         <v>1</v>
       </c>
       <c r="G265">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A266">
-        <v>2064</v>
+        <v>2282</v>
       </c>
       <c r="B266" s="1">
-        <v>45349.484930555547</v>
+        <v>45362.354004629633</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D266" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E266">
-        <v>3215</v>
+        <v>3120</v>
       </c>
       <c r="F266">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G266">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A267">
-        <v>2074</v>
+        <v>2285</v>
       </c>
       <c r="B267" s="1">
-        <v>45349.776145833333</v>
+        <v>45362.433796296304</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D267" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E267">
-        <v>2830</v>
+        <v>3231</v>
       </c>
       <c r="F267">
         <v>1</v>
       </c>
       <c r="G267">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A268">
-        <v>2083</v>
+        <v>2373</v>
       </c>
       <c r="B268" s="1">
-        <v>45350.384687500002</v>
+        <v>45368.741099537037</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D268" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E268">
-        <v>2846</v>
+        <v>3477</v>
       </c>
       <c r="F268">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G268">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A269">
-        <v>2135</v>
+        <v>2399</v>
       </c>
       <c r="B269" s="1">
-        <v>45352.732627314806</v>
+        <v>45370.014594907407</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D269" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E269">
-        <v>2833</v>
+        <v>2373</v>
       </c>
       <c r="F269">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G269">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A270">
-        <v>2198</v>
+        <v>2404</v>
       </c>
       <c r="B270" s="1">
-        <v>45356.725115740737</v>
+        <v>45370.086782407408</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D270" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E270">
-        <v>3475</v>
+        <v>2310</v>
       </c>
       <c r="F270">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G270">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A271">
-        <v>2213</v>
+        <v>2418</v>
       </c>
       <c r="B271" s="1">
-        <v>45357.559155092589</v>
+        <v>45370.662465277783</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D271" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E271">
-        <v>2836</v>
+        <v>2646</v>
       </c>
       <c r="F271">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G271">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A272">
-        <v>2248</v>
+        <v>2422</v>
       </c>
       <c r="B272" s="1">
-        <v>45359.527303240742</v>
+        <v>45370.796458333331</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D272" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E272">
-        <v>3010</v>
+        <v>2540</v>
       </c>
       <c r="F272">
         <v>0</v>
       </c>
       <c r="G272">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A273">
-        <v>2271</v>
+        <v>2426</v>
       </c>
       <c r="B273" s="1">
-        <v>45361.71707175926</v>
+        <v>45371.021990740737</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D273" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E273">
-        <v>3341</v>
+        <v>2930</v>
       </c>
       <c r="F273">
         <v>1</v>
       </c>
       <c r="G273">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274">
-        <v>2282</v>
+        <v>2431</v>
       </c>
       <c r="B274" s="1">
-        <v>45362.354004629633</v>
+        <v>45371.307013888887</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D274" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E274">
-        <v>3120</v>
+        <v>2458</v>
       </c>
       <c r="F274">
+        <v>0</v>
+      </c>
+      <c r="G274">
         <v>2</v>
-      </c>
-      <c r="G274">
-        <v>1</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A275">
-        <v>2285</v>
+        <v>2439</v>
       </c>
       <c r="B275" s="1">
-        <v>45362.433796296304</v>
+        <v>45371.509212962963</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D275" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E275">
-        <v>3231</v>
+        <v>3039</v>
       </c>
       <c r="F275">
         <v>1</v>
       </c>
       <c r="G275">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A276">
-        <v>2373</v>
+        <v>2468</v>
       </c>
       <c r="B276" s="1">
-        <v>45368.741099537037</v>
+        <v>45373.021099537043</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D276" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E276">
-        <v>3477</v>
+        <v>2928</v>
       </c>
       <c r="F276">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G276">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A277">
-        <v>2399</v>
+        <v>2482</v>
       </c>
       <c r="B277" s="1">
-        <v>45370.014594907407</v>
+        <v>45373.588067129633</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D277" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E277">
-        <v>2373</v>
+        <v>2964</v>
       </c>
       <c r="F277">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G277">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A278">
-        <v>2404</v>
+        <v>2489</v>
       </c>
       <c r="B278" s="1">
-        <v>45370.086782407408</v>
+        <v>45373.717581018522</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D278" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E278">
-        <v>2310</v>
+        <v>1692</v>
       </c>
       <c r="F278">
         <v>1</v>
       </c>
       <c r="G278">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A279">
-        <v>2418</v>
+        <v>2512</v>
       </c>
       <c r="B279" s="1">
-        <v>45370.662465277783</v>
+        <v>45374.943402777782</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D279" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E279">
-        <v>2646</v>
+        <v>3150</v>
       </c>
       <c r="F279">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G279">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A280">
-        <v>2422</v>
+        <v>2516</v>
       </c>
       <c r="B280" s="1">
-        <v>45370.796458333331</v>
+        <v>45375.138692129629</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D280" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E280">
-        <v>2540</v>
+        <v>2672</v>
       </c>
       <c r="F280">
         <v>0</v>
       </c>
       <c r="G280">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A281">
-        <v>2426</v>
+        <v>2528</v>
       </c>
       <c r="B281" s="1">
-        <v>45371.021990740737</v>
+        <v>45375.550740740742</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D281" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E281">
-        <v>2930</v>
+        <v>2877</v>
       </c>
       <c r="F281">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G281">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A282">
-        <v>2431</v>
+        <v>2542</v>
       </c>
       <c r="B282" s="1">
-        <v>45371.307013888887</v>
+        <v>45376.04383101852</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D282" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E282">
-        <v>2458</v>
+        <v>3379</v>
       </c>
       <c r="F282">
         <v>0</v>
       </c>
       <c r="G282">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A283">
-        <v>2439</v>
+        <v>2549</v>
       </c>
       <c r="B283" s="1">
-        <v>45371.509212962963</v>
+        <v>45376.678333333337</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D283" t="s">
         <v>562</v>
       </c>
       <c r="E283">
-        <v>3039</v>
+        <v>2789</v>
       </c>
       <c r="F283">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G283">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A284">
-        <v>2468</v>
+        <v>2571</v>
       </c>
       <c r="B284" s="1">
-        <v>45373.021099537043</v>
+        <v>45377.720370370371</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>563</v>
@@ -9902,21 +9837,21 @@
         <v>564</v>
       </c>
       <c r="E284">
-        <v>2928</v>
+        <v>2297</v>
       </c>
       <c r="F284">
         <v>0</v>
       </c>
       <c r="G284">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A285">
-        <v>2482</v>
+        <v>2605</v>
       </c>
       <c r="B285" s="1">
-        <v>45373.588067129633</v>
+        <v>45378.750752314823</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>565</v>
@@ -9925,21 +9860,21 @@
         <v>566</v>
       </c>
       <c r="E285">
-        <v>2964</v>
+        <v>2650</v>
       </c>
       <c r="F285">
         <v>1</v>
       </c>
       <c r="G285">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A286">
-        <v>2489</v>
+        <v>2607</v>
       </c>
       <c r="B286" s="1">
-        <v>45373.717581018522</v>
+        <v>45378.764768518522</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>567</v>
@@ -9948,21 +9883,21 @@
         <v>568</v>
       </c>
       <c r="E286">
-        <v>1692</v>
+        <v>2591</v>
       </c>
       <c r="F286">
         <v>1</v>
       </c>
       <c r="G286">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A287">
-        <v>2512</v>
+        <v>2610</v>
       </c>
       <c r="B287" s="1">
-        <v>45374.943402777782</v>
+        <v>45378.820057870369</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>569</v>
@@ -9971,21 +9906,21 @@
         <v>570</v>
       </c>
       <c r="E287">
-        <v>3150</v>
+        <v>2673</v>
       </c>
       <c r="F287">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G287">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A288">
-        <v>2516</v>
+        <v>2611</v>
       </c>
       <c r="B288" s="1">
-        <v>45375.138692129629</v>
+        <v>45378.820370370369</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>571</v>
@@ -9994,21 +9929,21 @@
         <v>572</v>
       </c>
       <c r="E288">
-        <v>2672</v>
+        <v>2368</v>
       </c>
       <c r="F288">
         <v>0</v>
       </c>
       <c r="G288">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A289">
-        <v>2528</v>
+        <v>2620</v>
       </c>
       <c r="B289" s="1">
-        <v>45375.550740740742</v>
+        <v>45378.891782407409</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>573</v>
@@ -10017,21 +9952,21 @@
         <v>574</v>
       </c>
       <c r="E289">
-        <v>2877</v>
+        <v>2912</v>
       </c>
       <c r="F289">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G289">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A290">
-        <v>2542</v>
+        <v>2656</v>
       </c>
       <c r="B290" s="1">
-        <v>45376.04383101852</v>
+        <v>45380.761932870373</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>575</v>
@@ -10040,102 +9975,102 @@
         <v>576</v>
       </c>
       <c r="E290">
-        <v>3379</v>
+        <v>2625</v>
       </c>
       <c r="F290">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G290">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A291">
-        <v>2549</v>
+        <v>2665</v>
       </c>
       <c r="B291" s="1">
-        <v>45376.678333333337</v>
+        <v>45381.046446759261</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>577</v>
       </c>
       <c r="D291" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E291">
-        <v>2789</v>
+        <v>2942</v>
       </c>
       <c r="F291">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G291">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A292">
-        <v>2571</v>
+        <v>2667</v>
       </c>
       <c r="B292" s="1">
-        <v>45377.720370370371</v>
+        <v>45381.109432870369</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D292" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E292">
-        <v>2297</v>
+        <v>3137</v>
       </c>
       <c r="F292">
         <v>0</v>
       </c>
       <c r="G292">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A293">
-        <v>2605</v>
+        <v>2668</v>
       </c>
       <c r="B293" s="1">
-        <v>45378.750752314823</v>
+        <v>45381.109513888892</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D293" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E293">
-        <v>2650</v>
+        <v>2970</v>
       </c>
       <c r="F293">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G293">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A294">
-        <v>2607</v>
+        <v>2683</v>
       </c>
       <c r="B294" s="1">
-        <v>45378.764768518522</v>
+        <v>45381.88113425926</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D294" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E294">
-        <v>2591</v>
+        <v>2850</v>
       </c>
       <c r="F294">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G294">
         <v>4</v>
@@ -10143,213 +10078,29 @@
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A295">
-        <v>2610</v>
+        <v>2697</v>
       </c>
       <c r="B295" s="1">
-        <v>45378.820057870369</v>
+        <v>45382.722881944443</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D295" t="s">
         <v>585</v>
       </c>
       <c r="E295">
-        <v>2673</v>
+        <v>3344</v>
       </c>
       <c r="F295">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G295">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A296">
-        <v>2611</v>
-      </c>
-      <c r="B296" s="1">
-        <v>45378.820370370369</v>
-      </c>
-      <c r="C296" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="D296" t="s">
-        <v>587</v>
-      </c>
-      <c r="E296">
-        <v>2368</v>
-      </c>
-      <c r="F296">
-        <v>0</v>
-      </c>
-      <c r="G296">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A297">
-        <v>2620</v>
-      </c>
-      <c r="B297" s="1">
-        <v>45378.891782407409</v>
-      </c>
-      <c r="C297" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="D297" t="s">
-        <v>589</v>
-      </c>
-      <c r="E297">
-        <v>2912</v>
-      </c>
-      <c r="F297">
-        <v>1</v>
-      </c>
-      <c r="G297">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A298">
-        <v>2656</v>
-      </c>
-      <c r="B298" s="1">
-        <v>45380.761932870373</v>
-      </c>
-      <c r="C298" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="D298" t="s">
-        <v>591</v>
-      </c>
-      <c r="E298">
-        <v>2625</v>
-      </c>
-      <c r="F298">
-        <v>1</v>
-      </c>
-      <c r="G298">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A299">
-        <v>2665</v>
-      </c>
-      <c r="B299" s="1">
-        <v>45381.046446759261</v>
-      </c>
-      <c r="C299" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="D299" t="s">
-        <v>593</v>
-      </c>
-      <c r="E299">
-        <v>2942</v>
-      </c>
-      <c r="F299">
-        <v>0</v>
-      </c>
-      <c r="G299">
         <v>4</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A300">
-        <v>2667</v>
-      </c>
-      <c r="B300" s="1">
-        <v>45381.109432870369</v>
-      </c>
-      <c r="C300" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="D300" t="s">
-        <v>595</v>
-      </c>
-      <c r="E300">
-        <v>3137</v>
-      </c>
-      <c r="F300">
-        <v>0</v>
-      </c>
-      <c r="G300">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A301">
-        <v>2668</v>
-      </c>
-      <c r="B301" s="1">
-        <v>45381.109513888892</v>
-      </c>
-      <c r="C301" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="D301" t="s">
-        <v>597</v>
-      </c>
-      <c r="E301">
-        <v>2970</v>
-      </c>
-      <c r="F301">
-        <v>0</v>
-      </c>
-      <c r="G301">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A302">
-        <v>2683</v>
-      </c>
-      <c r="B302" s="1">
-        <v>45381.88113425926</v>
-      </c>
-      <c r="C302" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="D302" t="s">
-        <v>599</v>
-      </c>
-      <c r="E302">
-        <v>2850</v>
-      </c>
-      <c r="F302">
-        <v>0</v>
-      </c>
-      <c r="G302">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A303">
-        <v>2697</v>
-      </c>
-      <c r="B303" s="1">
-        <v>45382.722881944443</v>
-      </c>
-      <c r="C303" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="D303" t="s">
-        <v>600</v>
-      </c>
-      <c r="E303">
-        <v>3344</v>
-      </c>
-      <c r="F303">
-        <v>2</v>
-      </c>
-      <c r="G303">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G303" xr:uid="{11F9F51D-90CE-470E-A078-80875014C3E8}"/>
+  <autoFilter ref="A1:G295" xr:uid="{F33CD2C8-CD88-4DD5-9FF5-279A63800069}"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
